--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_VALENCIA BASKET.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_VALENCIA BASKET.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9717</v>
+        <v>21.838</v>
       </c>
       <c r="E2" t="n">
-        <v>18.7139</v>
+        <v>22.7635</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7421</v>
+        <v>-0.9256</v>
       </c>
       <c r="G2" t="n">
         <v>17.986</v>
@@ -610,13 +610,13 @@
         <v>11.1463</v>
       </c>
       <c r="S2" t="n">
-        <v>-5.1146</v>
+        <v>-0.2485000000000002</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.6569</v>
+        <v>1.3928</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.4578</v>
+        <v>-1.6413</v>
       </c>
       <c r="V2" t="n">
         <v>8.422599999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0862</v>
+        <v>4.511</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7604</v>
+        <v>-0.8904999999999994</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3257</v>
+        <v>5.4016</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.04700000000000037</v>
+        <v>-4.8157</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0403</v>
+        <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0873</v>
+        <v>-6.265700000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1212</v>
+        <v>-0.2485000000000002</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5415</v>
+        <v>5.3414</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5798</v>
+        <v>-5.589700000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.1681</v>
+        <v>-4.5673</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4987</v>
+        <v>-3.8913</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.667</v>
+        <v>-0.6759000000000004</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9097999999999999</v>
+        <v>3.6395</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.5495</v>
+        <v>-9.7814</v>
       </c>
       <c r="R3" t="n">
-        <v>5.459300000000001</v>
+        <v>13.4209</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0649</v>
+        <v>1.8018</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0303</v>
+        <v>2.2818</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0344</v>
+        <v>-0.4801</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1583</v>
+        <v>3.8855</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1583</v>
+        <v>6.8574</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.9719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9208</v>
+        <v>2.8124</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4056000000000011</v>
+        <v>4.4872</v>
       </c>
       <c r="F4" t="n">
-        <v>4.326499999999999</v>
+        <v>-1.6748</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.8157</v>
+        <v>5.2574</v>
       </c>
       <c r="H4" t="n">
-        <v>1.45</v>
+        <v>1.7823</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.265700000000001</v>
+        <v>3.4752</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2485000000000002</v>
+        <v>7.9725</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3414</v>
+        <v>1.8386</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.589700000000001</v>
+        <v>6.1339</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.5673</v>
+        <v>-2.7148</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.8913</v>
+        <v>-0.05630000000000002</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6759000000000004</v>
+        <v>-2.6586</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6395</v>
+        <v>-2.2748</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9.7814</v>
+        <v>-5.914400000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>13.4209</v>
+        <v>3.6396</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2117</v>
+        <v>-0.01190000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7669</v>
+        <v>-0.4545</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.555</v>
+        <v>0.4424999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8855</v>
+        <v>-0.1581999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>6.8574</v>
+        <v>2.8837</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.9719</v>
+        <v>-3.0419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9924</v>
+        <v>2.5417</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0082</v>
+        <v>1.6706</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0007</v>
+        <v>0.8712</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5016</v>
+        <v>-0.04700000000000037</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6391</v>
+        <v>2.0403</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1407</v>
+        <v>-2.0873</v>
       </c>
       <c r="J5" t="n">
-        <v>1.84</v>
+        <v>5.1212</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8794000000000002</v>
+        <v>1.5415</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7195</v>
+        <v>3.5798</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3384</v>
+        <v>-5.1681</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7595000000000001</v>
+        <v>0.4987</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4211</v>
+        <v>-5.667</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5923</v>
+        <v>0.9097999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8671</v>
+        <v>-4.5495</v>
       </c>
       <c r="R5" t="n">
-        <v>5.4593</v>
+        <v>5.459300000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>6.561</v>
+        <v>1.5204</v>
       </c>
       <c r="T5" t="n">
-        <v>6.2744</v>
+        <v>0.9405</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2866</v>
+        <v>0.58</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.6623</v>
+        <v>0.1583</v>
       </c>
       <c r="W5" t="n">
-        <v>-5.2555</v>
+        <v>0.1583</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8858</v>
+        <v>0.1161000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9484</v>
+        <v>-3.5494</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0626</v>
+        <v>3.6655</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2574</v>
+        <v>1.5016</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7823</v>
+        <v>-1.6391</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4752</v>
+        <v>3.1407</v>
       </c>
       <c r="J6" t="n">
-        <v>7.9725</v>
+        <v>1.84</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8386</v>
+        <v>-0.8794000000000002</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1339</v>
+        <v>2.7195</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7148</v>
+        <v>-0.3384</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05630000000000002</v>
+        <v>-0.7595000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.6586</v>
+        <v>0.4211</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2748</v>
+        <v>1.5923</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.914400000000001</v>
+        <v>-3.8671</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6396</v>
+        <v>5.4593</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9387</v>
+        <v>3.6845</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9933999999999999</v>
+        <v>3.733</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05469999999999997</v>
+        <v>-0.0484</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1581999999999999</v>
+        <v>-6.6623</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8837</v>
+        <v>-5.2555</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.0419</v>
+        <v>-1.4068</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9925000000000004</v>
+        <v>0.1126</v>
       </c>
       <c r="E7" t="n">
-        <v>7.114100000000001</v>
+        <v>-2.7449</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.1217</v>
+        <v>2.8576</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2132</v>
+        <v>-1.6401</v>
       </c>
       <c r="H7" t="n">
-        <v>4.970599999999999</v>
+        <v>-2.0821</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.7575</v>
+        <v>0.4419999999999997</v>
       </c>
       <c r="J7" t="n">
-        <v>5.6496</v>
+        <v>-1.2404</v>
       </c>
       <c r="K7" t="n">
-        <v>7.1029</v>
+        <v>-1.3224</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4535</v>
+        <v>0.08210000000000028</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.436299999999999</v>
+        <v>-0.3997000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1322</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3039</v>
+        <v>0.3597999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1373</v>
+        <v>3.8671</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.5967</v>
+        <v>-2.5022</v>
       </c>
       <c r="R7" t="n">
-        <v>7.734</v>
+        <v>6.3692</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6137</v>
+        <v>2.7029</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6109</v>
+        <v>2.3861</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9971000000000001</v>
+        <v>0.3167</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.972</v>
+        <v>-4.8172</v>
       </c>
       <c r="W7" t="n">
-        <v>5.4505</v>
+        <v>-1.3885</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.422599999999999</v>
+        <v>-3.4287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5380999999999996</v>
+        <v>-0.6476000000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3105</v>
+        <v>1.7893</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7723</v>
+        <v>-2.4369</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6401</v>
+        <v>0.2203</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0821</v>
+        <v>3.0697</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4419999999999997</v>
+        <v>-2.8495</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2404</v>
+        <v>5.391500000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3224</v>
+        <v>3.4468</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08210000000000028</v>
+        <v>1.9447</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3997000000000001</v>
+        <v>-5.1713</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.377</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3597999999999999</v>
+        <v>-4.7943</v>
       </c>
       <c r="P8" t="n">
-        <v>3.8671</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5022</v>
+        <v>-5.0045</v>
       </c>
       <c r="R8" t="n">
-        <v>6.3692</v>
+        <v>5.0045</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0522</v>
+        <v>-1.4127</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8204</v>
+        <v>-0.2330000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2315000000000001</v>
+        <v>-1.1798</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.8172</v>
+        <v>0.5451000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.3885</v>
+        <v>1.6352</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.4287</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6365</v>
+        <v>-1.2681</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3179</v>
+        <v>4.9948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6815</v>
+        <v>-6.2629</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2224</v>
+        <v>1.2132</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1857</v>
+        <v>4.970599999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0367</v>
+        <v>-3.7575</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7559999999999998</v>
+        <v>5.6496</v>
       </c>
       <c r="K9" t="n">
-        <v>0.602</v>
+        <v>7.1029</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.358</v>
+        <v>-1.4535</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4663</v>
+        <v>-4.436299999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7876000000000001</v>
+        <v>-2.1322</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6787</v>
+        <v>-2.3039</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5923</v>
+        <v>1.1373</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3649</v>
+        <v>-6.5967</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9572</v>
+        <v>7.734</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3712</v>
+        <v>-0.6465999999999998</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1971</v>
+        <v>0.4916999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8259</v>
+        <v>-1.1382</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6352</v>
+        <v>-2.972</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>5.4505</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6352</v>
+        <v>-8.422599999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6978</v>
+        <v>-1.8641</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3061999999999996</v>
+        <v>-2.384</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0038</v>
+        <v>0.5199</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.2546</v>
+        <v>-2.2224</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5404</v>
+        <v>-0.1857</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.795</v>
+        <v>-2.0367</v>
       </c>
       <c r="J10" t="n">
-        <v>1.282</v>
+        <v>-0.7559999999999998</v>
       </c>
       <c r="K10" t="n">
-        <v>3.542899999999999</v>
+        <v>0.602</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2608</v>
+        <v>-1.358</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.5367</v>
+        <v>-1.4663</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.0025</v>
+        <v>-0.7876000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.5342</v>
+        <v>-0.6787</v>
       </c>
       <c r="P10" t="n">
-        <v>4.322</v>
+        <v>1.5923</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5022</v>
+        <v>-1.3649</v>
       </c>
       <c r="R10" t="n">
-        <v>6.8241</v>
+        <v>2.9572</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.9454</v>
+        <v>0.4011</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.9924</v>
+        <v>-0.2632</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04710000000000003</v>
+        <v>0.6643</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1802</v>
+        <v>-1.6352</v>
       </c>
       <c r="W10" t="n">
-        <v>4.518700000000001</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3386</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1913</v>
+        <v>-2.7758</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0114000000000003</v>
+        <v>0.9167999999999994</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2027</v>
+        <v>-3.692600000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2203</v>
+        <v>-7.2546</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0697</v>
+        <v>0.5404</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8495</v>
+        <v>-7.795</v>
       </c>
       <c r="J11" t="n">
-        <v>5.391500000000001</v>
+        <v>1.282</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4468</v>
+        <v>3.542899999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9447</v>
+        <v>-2.2608</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.1713</v>
+        <v>-8.5367</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.377</v>
+        <v>-3.0025</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.7943</v>
+        <v>-5.5342</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>4.322</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.0045</v>
+        <v>-2.5022</v>
       </c>
       <c r="R11" t="n">
-        <v>5.0045</v>
+        <v>6.8241</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.9565</v>
+        <v>-2.0234</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0108</v>
+        <v>-2.3819</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.9457</v>
+        <v>0.3584000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5451000000000001</v>
+        <v>2.1802</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6352</v>
+        <v>4.518700000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0901</v>
+        <v>-2.3386</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6717</v>
+        <v>-3.5512</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.199</v>
+        <v>-1.6602</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4728</v>
+        <v>-1.891</v>
       </c>
       <c r="G12" t="n">
         <v>-1.633</v>
@@ -1390,13 +1390,13 @@
         <v>0.9099</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5157</v>
+        <v>-0.395</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7301</v>
+        <v>-0.1913</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7855</v>
+        <v>-0.2037</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1583000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6266</v>
+        <v>-8.0701</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2459</v>
+        <v>-3.871099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.380799999999999</v>
+        <v>-4.198599999999999</v>
       </c>
       <c r="G13" t="n">
         <v>2.308</v>
@@ -1468,13 +1468,13 @@
         <v>9.553900000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2718</v>
+        <v>2.8285</v>
       </c>
       <c r="T13" t="n">
-        <v>3.988</v>
+        <v>2.3626</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2837999999999999</v>
+        <v>0.4657</v>
       </c>
       <c r="V13" t="n">
         <v>-6.382400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>8.487399999999999</v>
+        <v>13.7549</v>
       </c>
       <c r="E14" t="n">
-        <v>19.3673</v>
+        <v>21.5221</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.8798</v>
+        <v>-7.7666</v>
       </c>
       <c r="G14" t="n">
         <v>10.8737</v>
@@ -1519,16 +1519,16 @@
         <v>-16.9549</v>
       </c>
       <c r="J14" t="n">
-        <v>58.61099999999999</v>
+        <v>58.611</v>
       </c>
       <c r="K14" t="n">
-        <v>44.6047</v>
+        <v>44.60469999999999</v>
       </c>
       <c r="L14" t="n">
         <v>14.0069</v>
       </c>
       <c r="M14" t="n">
-        <v>-47.7371</v>
+        <v>-47.73709999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-16.7751</v>
@@ -1546,19 +1546,19 @@
         <v>78.47819999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9332</v>
+        <v>8.201099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>7.9102</v>
+        <v>10.0646</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.977099999999999</v>
+        <v>-1.8639</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.5939</v>
+        <v>-7.593900000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>29.04960000000001</v>
+        <v>29.0496</v>
       </c>
       <c r="X14" t="n">
         <v>-36.6436</v>
